--- a/artfynd/A 24299-2026 artfynd.xlsx
+++ b/artfynd/A 24299-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,8 +794,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134772335</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24299-2026 artfynd.xlsx
+++ b/artfynd/A 24299-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,53 +680,72 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134772335</v>
+        <v>135638392</v>
       </c>
       <c r="B2" t="n">
-        <v>58136</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fårtjärnen, Fårtjärnen, Vstm</t>
+          <t>Skommartjärnen, Ljusnarsbergs sn, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506406</v>
+        <v>506475</v>
       </c>
       <c r="R2" t="n">
-        <v>6636753</v>
+        <v>6636703</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +769,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,33 +785,523 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135638392</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135638493</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57801</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skommartjärnen, Ljusnarsbergs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>506475</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6636703</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135638493</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134772335</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fårtjärnen, Fårtjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>506406</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6636753</v>
+      </c>
+      <c r="S4" t="n">
+        <v>75</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134772335</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135638466</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skommartjärnen, Ljusnarsbergs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>506475</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6636703</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135638466</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135638506</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skommartjärnen, Ljusnarsbergs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>506475</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6636703</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135638506</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24299-2026 artfynd.xlsx
+++ b/artfynd/A 24299-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,53 +680,72 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134772335</v>
+        <v>135638392</v>
       </c>
       <c r="B2" t="n">
-        <v>58141</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fårtjärnen, Fårtjärnen, Vstm</t>
+          <t>Skommartjärnen, Ljusnarsbergs sn, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506406</v>
+        <v>506475</v>
       </c>
       <c r="R2" t="n">
-        <v>6636753</v>
+        <v>6636703</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +769,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,33 +785,523 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135638392</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135638493</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57801</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skommartjärnen, Ljusnarsbergs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>506475</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6636703</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135638493</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134772335</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fårtjärnen, Fårtjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>506406</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6636753</v>
+      </c>
+      <c r="S4" t="n">
+        <v>75</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134772335</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135638466</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skommartjärnen, Ljusnarsbergs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>506475</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6636703</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135638466</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135638506</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skommartjärnen, Ljusnarsbergs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>506475</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6636703</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135638506</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24299-2026 artfynd.xlsx
+++ b/artfynd/A 24299-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135638392</v>
       </c>
       <c r="B2" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>135638493</v>
       </c>
       <c r="B3" t="n">
-        <v>57801</v>
+        <v>57803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>135638466</v>
       </c>
       <c r="B5" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>135638506</v>
       </c>
       <c r="B6" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24299-2026 artfynd.xlsx
+++ b/artfynd/A 24299-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135638392</v>
       </c>
       <c r="B2" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>135638493</v>
       </c>
       <c r="B3" t="n">
-        <v>57803</v>
+        <v>57804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>135638466</v>
       </c>
       <c r="B5" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>135638506</v>
       </c>
       <c r="B6" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24299-2026 artfynd.xlsx
+++ b/artfynd/A 24299-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135638392</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>135638493</v>
       </c>
       <c r="B3" t="n">
-        <v>57804</v>
+        <v>57808</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>135638466</v>
       </c>
       <c r="B5" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>135638506</v>
       </c>
       <c r="B6" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24299-2026 artfynd.xlsx
+++ b/artfynd/A 24299-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135638392</v>
       </c>
       <c r="B2" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>135638493</v>
       </c>
       <c r="B3" t="n">
-        <v>57808</v>
+        <v>57809</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>135638466</v>
       </c>
       <c r="B5" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>135638506</v>
       </c>
       <c r="B6" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
